--- a/2026/public/games/Canada_Japan_Classification_Worlds_2026_W.xlsx
+++ b/2026/public/games/Canada_Japan_Classification_Worlds_2026_W.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmui\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmui\Claude Projects\goalball-dashboard\2026\public\games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4953B3FF-1EFF-43B0-9AD1-CE846772A475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D5EE81-487D-4E60-B613-66C9B968A382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="243">
   <si>
     <t>N#</t>
   </si>
@@ -80,9 +80,6 @@
     <t>T-START</t>
   </si>
   <si>
-    <t>Team B</t>
-  </si>
-  <si>
     <t>00:03</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>Skip</t>
   </si>
   <si>
-    <t>Team A</t>
-  </si>
-  <si>
     <t>00:32</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
     <t>Player 7</t>
   </si>
   <si>
-    <t>Goal Team A</t>
-  </si>
-  <si>
     <t>01:34</t>
   </si>
   <si>
@@ -155,9 +146,6 @@
     <t>02:28</t>
   </si>
   <si>
-    <t>Goal Team B</t>
-  </si>
-  <si>
     <t>02:47</t>
   </si>
   <si>
@@ -753,6 +741,18 @@
   </si>
   <si>
     <t>Note: The Category column in Sheet1 uses "Team A" / "Team B" regardless of team names above.</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Goal Canada</t>
+  </si>
+  <si>
+    <t>Opponent</t>
+  </si>
+  <si>
+    <t>Goal Opponent</t>
   </si>
 </sst>
 </file>
@@ -1129,9 +1129,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M185"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1145,7 +1144,7 @@
     <col min="12" max="13" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1227,7 +1226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1268,147 +1267,147 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J5">
         <v>2.5</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1417,1024 +1416,1024 @@
         <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
       <c r="K8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J10">
         <v>4</v>
       </c>
       <c r="K10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H11">
         <v>4</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J11">
         <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12">
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
       <c r="K12" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H13">
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13">
         <v>2.5</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J15">
         <v>4.5</v>
       </c>
       <c r="K15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H16">
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="J16">
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H17">
         <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J17">
         <v>4.5</v>
       </c>
       <c r="K17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H18">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="J18">
         <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H19">
         <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J19">
         <v>4.5</v>
       </c>
       <c r="K19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20">
         <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20">
         <v>3</v>
       </c>
       <c r="K20" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21">
         <v>2</v>
       </c>
       <c r="K21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22">
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J22">
         <v>2.5</v>
       </c>
       <c r="K22" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H23">
         <v>4</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J23">
         <v>3</v>
       </c>
       <c r="K23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J24">
         <v>3</v>
       </c>
       <c r="K24" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H25">
         <v>4</v>
       </c>
       <c r="I25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J25">
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J26">
         <v>1.5</v>
       </c>
       <c r="K26" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H27">
         <v>2</v>
       </c>
       <c r="I27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J27">
         <v>4.5</v>
       </c>
       <c r="K27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H28">
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J28">
         <v>2</v>
       </c>
       <c r="K28" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L28" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H29">
         <v>4</v>
       </c>
       <c r="I29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J29">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H30">
         <v>4</v>
       </c>
       <c r="I30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J30">
         <v>2.5</v>
       </c>
       <c r="K30" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H31">
         <v>4</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J31">
         <v>4.5</v>
       </c>
       <c r="K31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L31" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
         <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H32">
         <v>4</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J32">
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
         <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H33">
         <v>4</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J33">
         <v>3</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H34">
         <v>5</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -2443,36 +2442,36 @@
         <v>16</v>
       </c>
       <c r="L34" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H35">
         <v>5</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2481,1217 +2480,1217 @@
         <v>16</v>
       </c>
       <c r="L35" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H36">
         <v>4</v>
       </c>
       <c r="I36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J36">
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J37">
         <v>2.5</v>
       </c>
       <c r="K37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H38">
         <v>5</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J38">
         <v>4</v>
       </c>
       <c r="K38" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H39">
         <v>3</v>
       </c>
       <c r="I39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L39" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H40">
         <v>4</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J40">
         <v>4</v>
       </c>
       <c r="K40" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C41" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H41">
         <v>4</v>
       </c>
       <c r="I41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41">
         <v>2</v>
       </c>
       <c r="K41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L41" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H42">
         <v>4</v>
       </c>
       <c r="I42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J42">
         <v>3.5</v>
       </c>
       <c r="K42" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L42" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J43">
         <v>4</v>
       </c>
       <c r="K43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L43" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D44" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H44">
         <v>2</v>
       </c>
       <c r="I44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J44">
         <v>4</v>
       </c>
       <c r="K44" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H45">
         <v>4</v>
       </c>
       <c r="I45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J45">
         <v>2.5</v>
       </c>
       <c r="K45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D46" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H46">
         <v>5</v>
       </c>
       <c r="I46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J46">
         <v>2</v>
       </c>
       <c r="K46" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M46" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F47" t="s">
         <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H47">
         <v>3</v>
       </c>
       <c r="I47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H48">
         <v>4</v>
       </c>
       <c r="I48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E49" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H49">
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J49">
         <v>2</v>
       </c>
       <c r="K49" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L49" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J50">
         <v>4.5</v>
       </c>
       <c r="K50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L50" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51">
         <v>4</v>
       </c>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J51">
         <v>3</v>
       </c>
       <c r="K51" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L51" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J52">
         <v>4.5</v>
       </c>
       <c r="K52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L52" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D53" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J53">
         <v>5</v>
       </c>
       <c r="K53" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L53" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E54" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H54">
         <v>4</v>
       </c>
       <c r="I54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J54">
         <v>5</v>
       </c>
       <c r="K54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L54" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E55" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H55">
         <v>5</v>
       </c>
       <c r="I55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J55">
         <v>2.5</v>
       </c>
       <c r="K55" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L55" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J56">
         <v>3</v>
       </c>
       <c r="K56" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L56" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E57" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H57">
         <v>5</v>
       </c>
       <c r="I57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J57">
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L57" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E58" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H58">
         <v>3</v>
       </c>
       <c r="I58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L58" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H59">
         <v>4</v>
       </c>
       <c r="I59" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="J59">
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L59" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D60" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E60" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H60">
         <v>3</v>
       </c>
       <c r="I60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J60">
         <v>2</v>
       </c>
       <c r="K60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C61" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D61" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E61" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H61">
         <v>5</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J61">
         <v>3</v>
       </c>
       <c r="K61" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L61" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C62" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E62" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H62">
         <v>4</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L62" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D63" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E63" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J63">
         <v>4.5</v>
       </c>
       <c r="K63" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L63" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E64" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L64" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C65" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E65" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H65">
         <v>4</v>
       </c>
       <c r="I65" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="J65">
         <v>2</v>
       </c>
       <c r="K65" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L65" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E66" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H66">
         <v>5</v>
       </c>
       <c r="I66" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="J66">
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D67" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H67">
         <v>5</v>
       </c>
       <c r="I67" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J67" t="s">
         <v>16</v>
@@ -3700,36 +3699,36 @@
         <v>16</v>
       </c>
       <c r="L67" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E68" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H68">
         <v>3</v>
       </c>
       <c r="I68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J68">
         <v>6</v>
@@ -3738,252 +3737,252 @@
         <v>16</v>
       </c>
       <c r="L68" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D69" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E69" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H69">
         <v>3</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J69">
         <v>3</v>
       </c>
       <c r="K69" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L69" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D70" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E70" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H70">
         <v>5</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J70">
         <v>1.5</v>
       </c>
       <c r="K70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L70" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>38</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C71" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D71" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E71" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H71">
         <v>5</v>
       </c>
       <c r="I71" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J71">
         <v>2</v>
       </c>
       <c r="K71" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L71" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E72" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H72">
         <v>3</v>
       </c>
       <c r="I72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J72">
         <v>4.5</v>
       </c>
       <c r="K72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L72" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C73" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D73" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E73" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H73">
         <v>3</v>
       </c>
       <c r="I73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J73">
         <v>3</v>
       </c>
       <c r="K73" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L73" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>35</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C74" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E74" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H74">
         <v>2</v>
       </c>
       <c r="I74" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J74">
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L74" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E75" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
@@ -3995,7 +3994,7 @@
         <v>16</v>
       </c>
       <c r="I75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
         <v>16</v>
@@ -4004,758 +4003,758 @@
         <v>16</v>
       </c>
       <c r="L75" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C76" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D76" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E76" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F76" t="s">
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H76">
         <v>5</v>
       </c>
       <c r="I76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J76">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L76" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C77" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E77" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H77">
         <v>5</v>
       </c>
       <c r="I77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J77">
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L77" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D78" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E78" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J78">
         <v>3</v>
       </c>
       <c r="K78" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L78" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D79" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E79" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H79">
         <v>2</v>
       </c>
       <c r="I79" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J79">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L79" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C80" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E80" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J80">
         <v>4</v>
       </c>
       <c r="K80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L80" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>39</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C81" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D81" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E81" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F81" t="s">
         <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H81">
         <v>4</v>
       </c>
       <c r="I81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J81">
         <v>4</v>
       </c>
       <c r="K81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L81" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C82" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D82" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F82" t="s">
         <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H82">
         <v>3</v>
       </c>
       <c r="I82" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J82">
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L82" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>46</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C83" t="s">
+        <v>108</v>
+      </c>
+      <c r="D83" t="s">
         <v>112</v>
       </c>
-      <c r="D83" t="s">
-        <v>116</v>
-      </c>
       <c r="E83" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H83">
         <v>5</v>
       </c>
       <c r="I83" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="J83">
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L83" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>40</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E84" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H84">
         <v>5</v>
       </c>
       <c r="I84" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="J84">
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L84" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>47</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C85" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D85" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F85" t="s">
         <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H85">
         <v>5</v>
       </c>
       <c r="I85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J85">
         <v>3</v>
       </c>
       <c r="K85" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L85" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E86" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F86" t="s">
         <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H86">
         <v>4</v>
       </c>
       <c r="I86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J86">
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L86" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>48</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C87" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D87" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E87" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F87" t="s">
         <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H87">
         <v>2</v>
       </c>
       <c r="I87" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J87">
         <v>4</v>
       </c>
       <c r="K87" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L87" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C88" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E88" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F88" t="s">
         <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H88">
         <v>2</v>
       </c>
       <c r="I88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J88">
         <v>4.5</v>
       </c>
       <c r="K88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L88" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C89" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E89" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F89" t="s">
         <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H89">
         <v>5</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J89">
         <v>2.5</v>
       </c>
       <c r="K89" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L89" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>43</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C90" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E90" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F90" t="s">
         <v>16</v>
       </c>
       <c r="G90" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H90">
         <v>2</v>
       </c>
       <c r="I90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J90">
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D91" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E91" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F91" t="s">
         <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H91">
         <v>4</v>
       </c>
       <c r="I91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J91">
         <v>5</v>
       </c>
       <c r="K91" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L91" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F92" t="s">
         <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H92">
         <v>5</v>
       </c>
       <c r="I92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J92">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L92" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>51</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E93" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H93">
         <v>5</v>
       </c>
       <c r="I93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J93">
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L93" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E94" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F94" t="s">
         <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H94">
         <v>2</v>
       </c>
       <c r="I94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J94">
         <v>2.5</v>
       </c>
       <c r="K94" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L94" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>52</v>
       </c>
       <c r="B95" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C95" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D95" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E95" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F95" t="s">
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J95">
         <v>6</v>
@@ -4764,416 +4763,416 @@
         <v>16</v>
       </c>
       <c r="L95" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>46</v>
       </c>
       <c r="B96" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C96" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D96" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E96" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F96" t="s">
         <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H96">
         <v>5</v>
       </c>
       <c r="I96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J96">
         <v>1.5</v>
       </c>
       <c r="K96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L96" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>47</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D97" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E97" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F97" t="s">
         <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J97">
         <v>4</v>
       </c>
       <c r="K97" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L97" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>54</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C98" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E98" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F98" t="s">
         <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H98">
         <v>5</v>
       </c>
       <c r="I98" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J98">
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L98" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>48</v>
       </c>
       <c r="B99" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C99" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E99" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F99" t="s">
         <v>16</v>
       </c>
       <c r="G99" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H99">
         <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="J99">
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L99" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>55</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C100" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E100" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F100" t="s">
         <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H100">
         <v>5</v>
       </c>
       <c r="I100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J100">
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L100" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>49</v>
       </c>
       <c r="B101" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C101" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D101" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E101" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F101" t="s">
         <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H101">
         <v>3</v>
       </c>
       <c r="I101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J101">
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L101" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>56</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C102" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E102" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F102" t="s">
         <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H102">
         <v>5</v>
       </c>
       <c r="I102" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="J102">
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L102" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C103" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D103" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E103" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F103" t="s">
         <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H103">
         <v>2</v>
       </c>
       <c r="I103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J103">
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L103" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>57</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C104" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D104" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E104" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F104" t="s">
         <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H104">
         <v>2</v>
       </c>
       <c r="I104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J104">
         <v>1.5</v>
       </c>
       <c r="K104" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L104" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>51</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D105" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E105" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F105" t="s">
         <v>16</v>
       </c>
       <c r="G105" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H105">
         <v>5</v>
       </c>
       <c r="I105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J105">
         <v>2.5</v>
       </c>
       <c r="K105" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L105" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>58</v>
       </c>
       <c r="B106" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C106" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E106" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F106" t="s">
         <v>16</v>
       </c>
       <c r="G106" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H106">
         <v>5</v>
       </c>
       <c r="I106" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -5182,492 +5181,492 @@
         <v>16</v>
       </c>
       <c r="L106" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C107" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D107" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E107" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F107" t="s">
         <v>16</v>
       </c>
       <c r="G107" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H107">
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J107">
         <v>4</v>
       </c>
       <c r="K107" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L107" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>59</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C108" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E108" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F108" t="s">
         <v>16</v>
       </c>
       <c r="G108" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H108">
         <v>5</v>
       </c>
       <c r="I108" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J108">
         <v>2.5</v>
       </c>
       <c r="K108" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L108" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C109" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E109" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F109" t="s">
         <v>16</v>
       </c>
       <c r="G109" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H109">
         <v>4</v>
       </c>
       <c r="I109" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J109">
         <v>3</v>
       </c>
       <c r="K109" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L109" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>60</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C110" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E110" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F110" t="s">
         <v>16</v>
       </c>
       <c r="G110" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H110">
         <v>4</v>
       </c>
       <c r="I110" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J110">
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L110" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D111" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E111" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F111" t="s">
         <v>16</v>
       </c>
       <c r="G111" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H111">
         <v>2</v>
       </c>
       <c r="I111" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J111">
         <v>4</v>
       </c>
       <c r="K111" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L111" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>61</v>
       </c>
       <c r="B112" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D112" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F112" t="s">
         <v>16</v>
       </c>
       <c r="G112" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H112">
         <v>5</v>
       </c>
       <c r="I112" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J112">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L112" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C113" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D113" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F113" t="s">
         <v>16</v>
       </c>
       <c r="G113" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H113">
         <v>1</v>
       </c>
       <c r="I113" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J113">
         <v>3.5</v>
       </c>
       <c r="K113" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L113" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>62</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E114" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F114" t="s">
         <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H114">
         <v>2</v>
       </c>
       <c r="I114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J114">
         <v>2.5</v>
       </c>
       <c r="K114" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L114" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>56</v>
       </c>
       <c r="B115" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C115" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D115" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E115" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F115" t="s">
         <v>16</v>
       </c>
       <c r="G115" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H115">
         <v>5</v>
       </c>
       <c r="I115" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J115">
         <v>4.5</v>
       </c>
       <c r="K115" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L115" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>63</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C116" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D116" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E116" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
       </c>
       <c r="G116" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H116">
         <v>2</v>
       </c>
       <c r="I116" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J116">
         <v>4</v>
       </c>
       <c r="K116" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L116" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>57</v>
       </c>
       <c r="B117" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C117" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D117" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E117" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F117" t="s">
         <v>16</v>
       </c>
       <c r="G117" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H117">
         <v>4</v>
       </c>
       <c r="I117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J117">
         <v>4</v>
       </c>
       <c r="K117" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L117" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>64</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C118" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D118" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E118" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F118" t="s">
         <v>16</v>
       </c>
       <c r="G118" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H118">
         <v>3</v>
       </c>
       <c r="I118" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J118">
         <v>3</v>
       </c>
       <c r="K118" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L118" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>58</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C119" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D119" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E119" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F119" t="s">
         <v>16</v>
       </c>
       <c r="G119" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H119">
         <v>4</v>
       </c>
       <c r="I119" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J119">
         <v>6</v>
@@ -5676,74 +5675,74 @@
         <v>16</v>
       </c>
       <c r="L119" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>65</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C120" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D120" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E120" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F120" t="s">
         <v>16</v>
       </c>
       <c r="G120" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H120">
         <v>2</v>
       </c>
       <c r="I120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J120">
         <v>2.5</v>
       </c>
       <c r="K120" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L120" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>59</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C121" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D121" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E121" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F121" t="s">
         <v>16</v>
       </c>
       <c r="G121" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H121">
         <v>5</v>
       </c>
       <c r="I121" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -5752,188 +5751,188 @@
         <v>16</v>
       </c>
       <c r="L121" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>66</v>
       </c>
       <c r="B122" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C122" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D122" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E122" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F122" t="s">
         <v>16</v>
       </c>
       <c r="G122" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H122">
         <v>4</v>
       </c>
       <c r="I122" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J122">
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L122" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>60</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C123" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D123" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E123" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F123" t="s">
         <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H123">
         <v>1</v>
       </c>
       <c r="I123" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J123">
         <v>4</v>
       </c>
       <c r="K123" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L123" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>67</v>
       </c>
       <c r="B124" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C124" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D124" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E124" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F124" t="s">
         <v>16</v>
       </c>
       <c r="G124" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H124">
         <v>2</v>
       </c>
       <c r="I124" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J124">
         <v>4.5</v>
       </c>
       <c r="K124" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L124" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>61</v>
       </c>
       <c r="B125" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C125" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D125" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E125" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F125" t="s">
         <v>16</v>
       </c>
       <c r="G125" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H125">
         <v>5</v>
       </c>
       <c r="I125" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J125">
         <v>1.5</v>
       </c>
       <c r="K125" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L125" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>68</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C126" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D126" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E126" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F126" t="s">
         <v>16</v>
       </c>
       <c r="G126" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H126">
         <v>1</v>
       </c>
       <c r="I126" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J126">
         <v>6</v>
@@ -5942,454 +5941,454 @@
         <v>16</v>
       </c>
       <c r="L126" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>62</v>
       </c>
       <c r="B127" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C127" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D127" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E127" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F127" t="s">
         <v>16</v>
       </c>
       <c r="G127" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H127">
         <v>1</v>
       </c>
       <c r="I127" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J127">
         <v>1.5</v>
       </c>
       <c r="K127" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L127" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C128" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D128" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E128" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F128" t="s">
         <v>16</v>
       </c>
       <c r="G128" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H128">
         <v>4</v>
       </c>
       <c r="I128" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J128">
         <v>1.5</v>
       </c>
       <c r="K128" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L128" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>63</v>
       </c>
       <c r="B129" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C129" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D129" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E129" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F129" t="s">
         <v>16</v>
       </c>
       <c r="G129" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H129">
         <v>4</v>
       </c>
       <c r="I129" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J129">
         <v>2.5</v>
       </c>
       <c r="K129" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L129" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>70</v>
       </c>
       <c r="B130" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C130" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D130" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E130" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F130" t="s">
         <v>16</v>
       </c>
       <c r="G130" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H130">
         <v>3</v>
       </c>
       <c r="I130" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J130">
         <v>2.5</v>
       </c>
       <c r="K130" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L130" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>64</v>
       </c>
       <c r="B131" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C131" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D131" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E131" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F131" t="s">
         <v>16</v>
       </c>
       <c r="G131" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H131">
         <v>4</v>
       </c>
       <c r="I131" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J131">
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L131" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>71</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C132" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D132" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E132" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F132" t="s">
         <v>16</v>
       </c>
       <c r="G132" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H132">
         <v>4</v>
       </c>
       <c r="I132" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J132">
         <v>3.5</v>
       </c>
       <c r="K132" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L132" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>65</v>
       </c>
       <c r="B133" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C133" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D133" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E133" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
       </c>
       <c r="G133" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H133">
         <v>5</v>
       </c>
       <c r="I133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J133">
         <v>1.5</v>
       </c>
       <c r="K133" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L133" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>72</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C134" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D134" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E134" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F134" t="s">
         <v>16</v>
       </c>
       <c r="G134" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H134">
         <v>1</v>
       </c>
       <c r="I134" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J134">
         <v>3.5</v>
       </c>
       <c r="K134" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L134" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>66</v>
       </c>
       <c r="B135" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C135" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D135" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E135" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F135" t="s">
         <v>16</v>
       </c>
       <c r="G135" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H135">
         <v>2</v>
       </c>
       <c r="I135" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J135">
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L135" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>73</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C136" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D136" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E136" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F136" t="s">
         <v>16</v>
       </c>
       <c r="G136" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H136">
         <v>5</v>
       </c>
       <c r="I136" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J136">
         <v>2.5</v>
       </c>
       <c r="K136" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L136" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>67</v>
       </c>
       <c r="B137" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C137" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D137" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E137" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F137" t="s">
         <v>16</v>
       </c>
       <c r="G137" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H137">
         <v>4</v>
       </c>
       <c r="I137" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J137">
         <v>1</v>
       </c>
       <c r="K137" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L137" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>74</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C138" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D138" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E138" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F138" t="s">
         <v>16</v>
       </c>
       <c r="G138" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H138">
         <v>5</v>
       </c>
       <c r="I138" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -6398,758 +6397,758 @@
         <v>16</v>
       </c>
       <c r="L138" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>68</v>
       </c>
       <c r="B139" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D139" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E139" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F139" t="s">
         <v>16</v>
       </c>
       <c r="G139" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H139">
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J139">
         <v>3</v>
       </c>
       <c r="K139" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L139" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>75</v>
       </c>
       <c r="B140" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C140" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D140" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E140" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F140" t="s">
         <v>16</v>
       </c>
       <c r="G140" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H140">
         <v>5</v>
       </c>
       <c r="I140" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J140">
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L140" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>69</v>
       </c>
       <c r="B141" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C141" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D141" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E141" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F141" t="s">
         <v>16</v>
       </c>
       <c r="G141" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H141">
         <v>4</v>
       </c>
       <c r="I141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J141">
         <v>1.5</v>
       </c>
       <c r="K141" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L141" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>77</v>
       </c>
       <c r="B142" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C142" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D142" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E142" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F142" t="s">
         <v>16</v>
       </c>
       <c r="G142" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H142">
         <v>4</v>
       </c>
       <c r="I142" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="J142">
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L142" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>70</v>
       </c>
       <c r="B143" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C143" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D143" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E143" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F143" t="s">
         <v>16</v>
       </c>
       <c r="G143" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H143">
         <v>4</v>
       </c>
       <c r="I143" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J143">
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L143" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>78</v>
       </c>
       <c r="B144" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C144" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D144" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E144" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F144" t="s">
         <v>16</v>
       </c>
       <c r="G144" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H144">
         <v>4</v>
       </c>
       <c r="I144" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J144">
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L144" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>71</v>
       </c>
       <c r="B145" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C145" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D145" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E145" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F145" t="s">
         <v>16</v>
       </c>
       <c r="G145" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H145">
         <v>4</v>
       </c>
       <c r="I145" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J145">
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L145" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>79</v>
       </c>
       <c r="B146" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C146" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D146" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E146" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F146" t="s">
         <v>16</v>
       </c>
       <c r="G146" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H146">
         <v>4</v>
       </c>
       <c r="I146" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J146">
         <v>2.5</v>
       </c>
       <c r="K146" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L146" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>72</v>
       </c>
       <c r="B147" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C147" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E147" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F147" t="s">
         <v>16</v>
       </c>
       <c r="G147" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H147">
         <v>3</v>
       </c>
       <c r="I147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J147">
         <v>2</v>
       </c>
       <c r="K147" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L147" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>80</v>
       </c>
       <c r="B148" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C148" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D148" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E148" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F148" t="s">
         <v>16</v>
       </c>
       <c r="G148" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H148">
         <v>4</v>
       </c>
       <c r="I148" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J148">
         <v>3.5</v>
       </c>
       <c r="K148" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L148" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>73</v>
       </c>
       <c r="B149" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C149" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D149" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E149" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F149" t="s">
         <v>16</v>
       </c>
       <c r="G149" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H149">
         <v>4</v>
       </c>
       <c r="I149" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J149">
         <v>2.5</v>
       </c>
       <c r="K149" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L149" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>81</v>
       </c>
       <c r="B150" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C150" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D150" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E150" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F150" t="s">
         <v>16</v>
       </c>
       <c r="G150" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H150">
         <v>3</v>
       </c>
       <c r="I150" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J150">
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L150" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>74</v>
       </c>
       <c r="B151" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C151" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D151" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E151" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
       </c>
       <c r="G151" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H151">
         <v>4</v>
       </c>
       <c r="I151" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J151">
         <v>3.5</v>
       </c>
       <c r="K151" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L151" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>82</v>
       </c>
       <c r="B152" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C152" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D152" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E152" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F152" t="s">
         <v>16</v>
       </c>
       <c r="G152" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H152">
         <v>5</v>
       </c>
       <c r="I152" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J152">
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L152" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>75</v>
       </c>
       <c r="B153" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C153" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D153" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E153" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F153" t="s">
         <v>16</v>
       </c>
       <c r="G153" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H153">
         <v>4</v>
       </c>
       <c r="I153" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J153">
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L153" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>83</v>
       </c>
       <c r="B154" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C154" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D154" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E154" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F154" t="s">
         <v>16</v>
       </c>
       <c r="G154" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H154">
         <v>4</v>
       </c>
       <c r="I154" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J154">
         <v>2</v>
       </c>
       <c r="K154" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L154" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>76</v>
       </c>
       <c r="B155" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C155" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D155" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E155" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F155" t="s">
         <v>16</v>
       </c>
       <c r="G155" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H155">
         <v>4</v>
       </c>
       <c r="I155" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J155">
         <v>4</v>
       </c>
       <c r="K155" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L155" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>84</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C156" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D156" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E156" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F156" t="s">
         <v>16</v>
       </c>
       <c r="G156" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H156">
         <v>5</v>
       </c>
       <c r="I156" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J156">
         <v>2</v>
       </c>
       <c r="K156" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L156" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>77</v>
       </c>
       <c r="B157" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C157" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D157" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E157" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F157" t="s">
         <v>16</v>
       </c>
       <c r="G157" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H157">
         <v>2</v>
       </c>
       <c r="I157" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J157">
         <v>4.5</v>
       </c>
       <c r="K157" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L157" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>85</v>
       </c>
       <c r="B158" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C158" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D158" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E158" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F158" t="s">
         <v>16</v>
       </c>
       <c r="G158" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H158">
         <v>3</v>
       </c>
       <c r="I158" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -7158,1012 +7157,1012 @@
         <v>16</v>
       </c>
       <c r="L158" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>78</v>
       </c>
       <c r="B159" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C159" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D159" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E159" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F159" t="s">
         <v>16</v>
       </c>
       <c r="G159" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H159">
         <v>1</v>
       </c>
       <c r="I159" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J159">
         <v>1.5</v>
       </c>
       <c r="K159" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L159" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>86</v>
       </c>
       <c r="B160" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C160" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D160" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E160" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F160" t="s">
         <v>16</v>
       </c>
       <c r="G160" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H160">
         <v>2</v>
       </c>
       <c r="I160" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J160">
         <v>2.5</v>
       </c>
       <c r="K160" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L160" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>79</v>
       </c>
       <c r="B161" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C161" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D161" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E161" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F161" t="s">
         <v>16</v>
       </c>
       <c r="G161" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H161">
         <v>4</v>
       </c>
       <c r="I161" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J161">
         <v>3.5</v>
       </c>
       <c r="K161" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L161" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>87</v>
       </c>
       <c r="B162" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C162" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D162" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E162" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F162" t="s">
         <v>16</v>
       </c>
       <c r="G162" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H162">
         <v>5</v>
       </c>
       <c r="I162" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J162">
         <v>2.5</v>
       </c>
       <c r="K162" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L162" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>80</v>
       </c>
       <c r="B163" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C163" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D163" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E163" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F163" t="s">
         <v>16</v>
       </c>
       <c r="G163" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H163">
         <v>4</v>
       </c>
       <c r="I163" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J163">
         <v>2</v>
       </c>
       <c r="K163" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L163" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>88</v>
       </c>
       <c r="B164" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C164" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D164" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E164" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F164" t="s">
         <v>16</v>
       </c>
       <c r="G164" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H164">
         <v>2</v>
       </c>
       <c r="I164" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J164">
         <v>4</v>
       </c>
       <c r="K164" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L164" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>81</v>
       </c>
       <c r="B165" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C165" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D165" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E165" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F165" t="s">
         <v>16</v>
       </c>
       <c r="G165" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H165">
         <v>4</v>
       </c>
       <c r="I165" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J165">
         <v>4</v>
       </c>
       <c r="K165" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L165" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>89</v>
       </c>
       <c r="B166" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C166" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D166" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E166" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F166" t="s">
         <v>16</v>
       </c>
       <c r="G166" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H166">
         <v>4</v>
       </c>
       <c r="I166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J166">
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L166" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>82</v>
       </c>
       <c r="B167" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C167" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D167" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E167" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
       </c>
       <c r="G167" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H167">
         <v>2</v>
       </c>
       <c r="I167" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J167">
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L167" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>90</v>
       </c>
       <c r="B168" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C168" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D168" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E168" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F168" t="s">
         <v>16</v>
       </c>
       <c r="G168" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H168">
         <v>5</v>
       </c>
       <c r="I168" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J168">
         <v>2</v>
       </c>
       <c r="K168" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L168" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>83</v>
       </c>
       <c r="B169" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C169" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D169" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E169" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F169" t="s">
         <v>16</v>
       </c>
       <c r="G169" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H169">
         <v>4</v>
       </c>
       <c r="I169" t="s">
+        <v>21</v>
+      </c>
+      <c r="J169">
+        <v>2</v>
+      </c>
+      <c r="K169" t="s">
         <v>22</v>
       </c>
-      <c r="J169">
-        <v>2</v>
-      </c>
-      <c r="K169" t="s">
-        <v>23</v>
-      </c>
       <c r="L169" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>91</v>
       </c>
       <c r="B170" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C170" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D170" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E170" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F170" t="s">
         <v>16</v>
       </c>
       <c r="G170" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H170">
         <v>2</v>
       </c>
       <c r="I170" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J170">
         <v>2</v>
       </c>
       <c r="K170" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L170" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>84</v>
       </c>
       <c r="B171" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C171" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D171" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E171" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F171" t="s">
         <v>16</v>
       </c>
       <c r="G171" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H171">
         <v>2</v>
       </c>
       <c r="I171" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J171">
         <v>2.5</v>
       </c>
       <c r="K171" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L171" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>92</v>
       </c>
       <c r="B172" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C172" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D172" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E172" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F172" t="s">
         <v>16</v>
       </c>
       <c r="G172" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H172">
         <v>2</v>
       </c>
       <c r="I172" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J172">
         <v>2</v>
       </c>
       <c r="K172" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L172" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>85</v>
       </c>
       <c r="B173" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C173" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D173" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E173" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
       </c>
       <c r="G173" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H173">
         <v>2</v>
       </c>
       <c r="I173" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J173">
         <v>4.5</v>
       </c>
       <c r="K173" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L173" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>93</v>
       </c>
       <c r="B174" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C174" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D174" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E174" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
       </c>
       <c r="G174" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H174">
         <v>4</v>
       </c>
       <c r="I174" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J174">
         <v>2</v>
       </c>
       <c r="K174" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L174" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>86</v>
       </c>
       <c r="B175" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C175" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D175" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E175" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F175" t="s">
         <v>16</v>
       </c>
       <c r="G175" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H175">
         <v>5</v>
       </c>
       <c r="I175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J175">
         <v>2.5</v>
       </c>
       <c r="K175" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L175" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>94</v>
       </c>
       <c r="B176" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C176" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D176" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E176" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F176" t="s">
         <v>16</v>
       </c>
       <c r="G176" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H176">
         <v>1</v>
       </c>
       <c r="I176" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J176">
         <v>2.5</v>
       </c>
       <c r="K176" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L176" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="177" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>87</v>
       </c>
       <c r="B177" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C177" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D177" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E177" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F177" t="s">
         <v>16</v>
       </c>
       <c r="G177" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H177">
         <v>2</v>
       </c>
       <c r="I177" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J177">
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L177" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="178" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>95</v>
       </c>
       <c r="B178" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C178" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D178" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E178" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F178" t="s">
         <v>16</v>
       </c>
       <c r="G178" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H178">
         <v>5</v>
       </c>
       <c r="I178" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J178">
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L178" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>88</v>
       </c>
       <c r="B179" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C179" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D179" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E179" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F179" t="s">
         <v>16</v>
       </c>
       <c r="G179" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H179">
         <v>2</v>
       </c>
       <c r="I179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J179">
         <v>2.5</v>
       </c>
       <c r="K179" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L179" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="180" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>96</v>
       </c>
       <c r="B180" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C180" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D180" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E180" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F180" t="s">
         <v>16</v>
       </c>
       <c r="G180" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H180">
         <v>2</v>
       </c>
       <c r="I180" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J180">
         <v>2</v>
       </c>
       <c r="K180" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L180" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>89</v>
       </c>
       <c r="B181" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C181" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D181" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E181" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F181" t="s">
         <v>16</v>
       </c>
       <c r="G181" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H181">
         <v>2</v>
       </c>
       <c r="I181" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J181">
         <v>2</v>
       </c>
       <c r="K181" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L181" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>97</v>
       </c>
       <c r="B182" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C182" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D182" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E182" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F182" t="s">
         <v>16</v>
       </c>
       <c r="G182" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H182">
         <v>2</v>
       </c>
       <c r="I182" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J182">
         <v>2</v>
       </c>
       <c r="K182" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L182" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>90</v>
       </c>
       <c r="B183" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="C183" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D183" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E183" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
       </c>
       <c r="G183" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H183">
         <v>4</v>
       </c>
       <c r="I183" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J183">
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L183" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>98</v>
       </c>
       <c r="B184" t="s">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="C184" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D184" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E184" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F184" t="s">
         <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H184">
         <v>4</v>
       </c>
       <c r="I184" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J184">
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L184" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>13</v>
       </c>
       <c r="B185" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C185" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D185" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E185" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F185" t="s">
         <v>16</v>
@@ -8191,16 +8190,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M185" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Team A"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M185" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M3 A5:F5 A4:J4 L4:M4 A7:F7 A6:J6 L6:M6 A9:F9 A8:J8 L8:M8 A11:F11 A10:J10 L10:M10 A13:F13 A12:J12 L12:M12 A15:F15 A14:J14 L14:M14 A17:F17 A16:J16 L16:M16 A19:F19 A18:J18 L18:M18 A21:F21 A20:J20 L20:M20 A23:F23 A22:J22 L22:M22 A25:F25 A24:J24 L24:M24 A27:F27 A26:J26 L26:M26 A29:F29 A28:J28 L28:M28 A31:F31 A30:J30 L30:M30 A34:M34 A32:J32 L32:M32 A37:F37 A36:J36 L36:M36 A39:F39 A38:J38 L38:M38 A41:F41 A40:J40 L40:M40 A43:F43 A42:J42 L42:M42 A45:F45 A44:J44 L44:M44 A48:F48 A46:J46 L46:M46 A47:J47 L47:M47 A50:F50 A49:J49 L49:M49 A52:F52 A51:J51 L51:M51 A54:F54 A53:J53 L53:M53 A56:F56 A55:J55 L55:M55 A58:F58 A57:J57 L57:M57 A61:F61 A59:J59 L59:M59 A63:F63 A62:J62 L62:M62 A67:M68 A64:J64 L64:M64 A65:J65 L65:M65 A70:F70 A69:J69 L69:M69 A72:F72 A71:J71 L71:M71 A75:M75 A73:J73 L73:M73 A78:F78 A77:J77 L77:M77 A81:F81 A79:J79 L79:M79 A84:F84 A82:J82 L82:M82 A83:J83 L83:M83 A86:F86 A85:J85 L85:M85 A88:F88 A87:J87 L87:M87 A90:F90 A89:J89 L89:M89 A92:F92 A91:J91 L91:M91 A95:M95 A93:J93 L93:M93 A99:F99 A98:J98 L98:M98 A101:F101 A100:J100 L100:M100 A103:F103 A102:J102 L102:M102 A106:M106 A104:J104 L104:M104 A109:F109 A108:J108 L108:M108 A111:F111 A110:J110 L110:M110 A113:F113 A112:J112 L112:M112 A115:F115 A114:J114 L114:M114 A117:F117 A116:J116 L116:M116 A119:F119 A118:J118 L118:M118 A121:F121 A120:J120 L120:M120 A123:F123 A122:J122 L122:M122 A126:M126 A124:J124 L124:M124 A129:F129 A128:J128 L128:M128 A131:F131 A130:J130 L130:M130 A133:F133 A132:J132 L132:M132 A135:F135 A134:J134 L134:M134 A138:M138 A136:J136 L136:M136 A141:F141 A140:J140 L140:M140 A143:F143 A142:J142 L142:M142 A145:F145 A144:J144 L144:M144 A147:F147 A146:J146 L146:M146 A149:F149 A148:J148 L148:M148 A151:F151 A150:J150 L150:M150 A153:F153 A152:J152 L152:M152 A155:F155 A154:J154 L154:M154 A158:M158 A156:J156 L156:M156 A161:F161 A160:J160 L160:M160 A163:F163 A162:J162 L162:M162 A165:F165 A164:J164 L164:M164 A167:F167 A166:J166 L166:M166 A169:F169 A168:J168 L168:M168 A171:F171 A170:J170 L170:M170 A173:F173 A172:J172 L172:M172 A175:F175 A174:J174 L174:M174 A177:F177 A176:J176 L176:M176 A179:F179 A178:J178 L178:M178 A181:F181 A180:J180 L180:M180 A183:F183 A182:J182 L182:M182 A185:M185 A184:J184 L184:M184 H5:M5 H7:M7 H9:M9 H11:M11 H13:M13 H15:M15 H17:M17 H19:M19 H21:M21 H23:M23 H25:M25 H27:M27 H29:M29 H31:M31 A33:F33 H33:M33 A35:F35 H35:M35 H37:M37 H39:M39 H41:M41 H43:M43 H45:M45 H48:M48 H50:M50 H52:M52 H54:M54 H56:M56 H58:M58 A60:F60 H60:M60 H61:M61 H63:M63 A66:F66 H66:M66 H70:M70 H72:M72 A74:F74 H74:M74 A76:F76 H76:M76 H78:M78 A80:F80 H80:M80 H81:M81 H84:M84 H86:M86 H88:M88 H90:M90 H92:M92 A94:F94 H94:M94 A97:F97 A96:F96 H96:M96 H97:M97 H99:M99 H101:M101 H103:M103 A105:F105 H105:M105 A107:F107 H107:M107 H109:M109 H111:M111 H113:M113 H115:M115 H117:M117 H119:M119 H121:M121 H123:M123 A125:F125 H125:M125 A127:F127 H127:M127 H129:M129 H131:M131 H133:M133 H135:M135 A137:F137 H137:M137 A139:F139 H139:M139 H141:M141 H143:M143 H145:M145 H147:M147 H149:M149 H151:M151 H153:M153 H155:M155 A157:F157 H157:M157 A159:F159 H159:M159 H161:M161 H163:M163 H165:M165 H167:M167 H169:M169 H171:M171 H173:M173 H175:M175 H177:M177 H179:M179 H181:M181 H183:M183" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M3 A5 A4 L4:M4 A7 A6 L6:M6 A9 A8 L8:M8 A11 A10 L10:M10 A13 A12 L12:M12 A15 A14 L14:M14 A17 A16 L16:M16 A19 A18 L18:M18 A21 A20 L20:M20 A23 A22 L22:M22 A25 A24 L24:M24 A27 A26 L26:M26 A29 A28 L28:M28 A31 A30 L30:M30 A34 A32 L32:M32 A37 A36 L36:M36 A39 A38 L38:M38 A41 A40 L40:M40 A43 A42 L42:M42 A45 A44 L44:M44 A48 A46 L46:M46 A47 L47:M47 A50 A49 L49:M49 A52 A51 L51:M51 A54 A53 L53:M53 A56 A55 L55:M55 A58 A57 L57:M57 A61 A59 L59:M59 A63 A62 L62:M62 A68:M68 A64 L64:M64 A65 L65:M65 A70 A69 L69:M69 A72 A71 L71:M71 A75 A73 L73:M73 A78 A77 L77:M77 A81 A79 L79:M79 A84 A82 L82:M82 A83 L83:M83 A86 A85 L85:M85 A88 A87 L87:M87 A90 A89 L89:M89 A92 A91 L91:M91 A95 A93 L93:M93 A99 A98 L98:M98 A101 A100 L100:M100 A103 A102 L102:M102 A106 A104 L104:M104 A109 A108 L108:M108 A111 A110 L110:M110 A113 A112 L112:M112 A115 A114 L114:M114 A117 A116 L116:M116 A119 A118 L118:M118 A121 A120 L120:M120 A123 A122 L122:M122 A126 A124 L124:M124 A129 A128 L128:M128 A131 A130 L130:M130 A133 A132 L132:M132 A135 A134 L134:M134 A138 A136 L136:M136 A141 A140 L140:M140 A143 A142 L142:M142 A145 A144 L144:M144 A147 A146 L146:M146 A149 A148 L148:M148 A151 A150 L150:M150 A153 A152 L152:M152 A155 A154 L154:M154 A158 A156 L156:M156 A161 A160 L160:M160 A163 A162 L162:M162 A165 A164 L164:M164 A167 A166 L166:M166 A169 A168 L168:M168 A171 A170 L170:M170 A173 A172 L172:M172 A175 A174 L174:M174 A177 A176 L176:M176 A179 A178 L178:M178 A181 A180 L180:M180 A183 A182 L182:M182 A185:M185 A184 L184:M184 H5:M5 H7:M7 H9 H11:M11 H13:M13 H15:M15 H17:M17 H19:M19 H21:M21 H23:M23 H25:M25 H27:M27 H29:M29 H31:M31 A33 H33:M33 A35 H35:M35 H37:M37 H39:M39 H41:M41 H43:M43 H45:M45 H48:M48 H50:M50 H52:M52 H54:M54 H56:M56 H58:M58 A60 H60:M60 H61:M61 H63:M63 A66 H66 H70:M70 H72:M72 A74 H74:M74 A76 H76:M76 H78:M78 A80 H80:M80 H81:M81 H84 H86:M86 H88:M88 H90:M90 H92:M92 A94 H94:M94 A97 A96 H96:M96 H97:M97 H99 H101:M101 H103:M103 A105 H105:M105 A107 H107:M107 H109:M109 H111:M111 H113:M113 H115:M115 H117:M117 H119:M119 H121:M121 H123:M123 A125 H125:M125 A127 H127:M127 H129:M129 H131:M131 H133:M133 H135:M135 A137 H137:M137 A139 H139:M139 H141:M141 H143:M143 H145:M145 H147:M147 H149:M149 H151:M151 H153:M153 H155:M155 A157 H157:M157 A159 H159:M159 H161:M161 H163:M163 H165:M165 H167:M167 H169:M169 H171:M171 H173:M173 H175:M175 H177:M177 H179:M179 H181:M181 H183:M183 C5:F5 C7:F7 C9:F9 J9:M9 C11:F11 C13:F13 C15:F15 C17:F17 C19:F19 C21:F21 C23:F23 C25:F25 C27:F27 C29:F29 C31:F31 C33:F33 C35:F35 C37:F37 C39:F39 C41:F41 C43:F43 C45:F45 C48:F48 C50:F50 C52:F52 C54:F54 C56:F56 C58:F58 C60:F60 C61:F61 C63:F63 C66:F66 J66:M66 C70:F70 C72:F72 C74:F74 C76:F76 C78:F78 C80:F80 C81:F81 C84:F84 J84:M84 C86:F86 C88:F88 C90:F90 C92:F92 C94:F94 C96:F96 C97:F97 C99:F99 J99:M99 C101:F101 C103:F103 C105:F105 C107:F107 C109:F109 C111:F111 C113:F113 C115:F115 C117:F117 C119:F119 C121:F121 C123:F123 C125:F125 C127:F127 C129:F129 C131:F131 C133:F133 C135:F135 C137:F137 C139:F139 C141:F141 C143:F143 C145:F145 C147:F147 C149:F149 C151:F151 C153:F153 C155:F155 C157:F157 C159:F159 C161:F161 C163:F163 C165:F165 C167:F167 C169:F169 C171:F171 C173:F173 C175:F175 C177:F177 C179:F179 C181:F181 C183:F183 C4:J4 C6:J6 C8:J8 C10:J10 C12:J12 C14:J14 C16:H16 J16 C18:H18 J18 C20:J20 C22:J22 C24:J24 C26:J26 C28:J28 C30:J30 C32:J32 C34:M34 C36:J36 C38:J38 C40:J40 C42:J42 C44:J44 C46:J46 C47:J47 C49:J49 C51:J51 C53:J53 C55:J55 C57:J57 C59:H59 J59 C62:J62 C64:J64 C65:H65 J65 A67 C67:M67 C69:J69 C71:J71 C73:J73 C75:M75 C77:J77 C79:J79 C82:J82 C83:H83 J83 C85:J85 C87:J87 C89:J89 C91:J91 C93:J93 C95:M95 C98:J98 C100:J100 C102:H102 J102 C104:J104 C106:M106 C108:J108 C110:J110 C112:J112 C114:J114 C116:J116 C118:J118 C120:J120 C122:J122 C124:J124 C126:M126 C128:J128 C130:J130 C132:J132 C134:J134 C136:J136 C138:M138 C140:J140 C142:H142 J142 C144:J144 C146:J146 C148:J148 C150:J150 C152:J152 C154:J154 C156:J156 C158:M158 C160:J160 C162:J162 C164:J164 C166:J166 C168:J168 C170:J170 C172:J172 C174:J174 C176:J176 C178:J178 C180:J180 C182:J182 C184:J184" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8208,7 +8201,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -8216,163 +8209,163 @@
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" t="s">
         <v>225</v>
       </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>226</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
         <v>227</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>228</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>229</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>228</v>
       </c>
-      <c r="D4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>230</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>231</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>230</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>232</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>233</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" t="s">
         <v>232</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>234</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>235</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>234</v>
       </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>236</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>237</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>236</v>
       </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>238</v>
-      </c>
-      <c r="B9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" t="s">
-        <v>240</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>242</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
